--- a/www/download/COUNTRY.ITA.WIOD16.xlsx
+++ b/www/download/COUNTRY.ITA.WIOD16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>Itália</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.0827197921178</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>1.11656989727557</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>1.0575296108291</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.281</t>
+          <t>0.884016973125884</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>0.803923144947343</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>0.803793907242183</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>0.796431984708506</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.408</t>
+          <t>0.729660707770887</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>0.67990209409845</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>0.71694866647548</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>0.75431847325941</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.504</t>
+          <t>0.718390804597701</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.778331257783312</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.484</t>
+          <t>0.75295534974776</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>0.75273011658591</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>23.021</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>23.473</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>23.867</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>24.218</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>24.365</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>24.501</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>24.984</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>25.295</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>25.349</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>24.926</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>24.766</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>24.843</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>24.765</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>24.323</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>24.368</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>16.665</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>17.047</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>17.415</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>17.622</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>17.666</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>17.96</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>18.357</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>18.64</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>18.77</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>18.544</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>18.342</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>18.426</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>18.394</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>18.082</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>18.127</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>39420.189</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>39936.347</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>40264.378</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>40403.117</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>40766.721</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>40687.65</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>41694.096</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>42227.49</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>42385.025</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>40818.254</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>40514.528</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>40619.552</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>39574.135</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>38497.084</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>38582.425</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>28269.982</t>
+          <t>57381080682.1164</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>28718.064</t>
+          <t>57046837537.975</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>29107.791</t>
+          <t>56691352401.5449</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>29121.067</t>
+          <t>58465236262.737</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>29263.41</t>
+          <t>61114214918.3844</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>29569.637</t>
+          <t>60786784776.6433</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>30318.697</t>
+          <t>64925922607.9222</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>30783.622</t>
+          <t>64655584213.9407</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>31022.793</t>
+          <t>65196519275.1371</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>29969.796</t>
+          <t>56568394111.327</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>29636.325</t>
+          <t>60810128359.3861</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>29756.257</t>
+          <t>65917051164.6911</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>29059.891</t>
+          <t>59195605651.9123</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>28323.992</t>
+          <t>56860544837.6838</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>28416.143</t>
+          <t>56372667335.3362</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>15350446824.2959</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15927908894.9524</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>16734048714.2276</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>18393313889.282</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>19713873554.7992</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>19816016553.1756</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>20853089577.3987</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>19759700666.9134</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>20000311927.5603</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>17936123262.8955</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>17080778269.0785</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>17455212834.0171</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>15359734882.7878</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>14944986550.5006</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>15234394318.998</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1457871.23080915</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1454223.81670625</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1333932.97036807</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1137485.99690224</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1034661.2134214</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>988667.445825158</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>970334.501023298</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>834813.335423087</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>770150.168884351</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>850564.101463614</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>891038.455798176</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>870739.013450497</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>882010.22008138</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>834353.046764042</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>841217.434253496</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>154049.315835451</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>154065.744538339</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>154501.27609476</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>167962.567309157</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>187746.751160567</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>201395.421903187</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>216244.162715631</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>246518.783314233</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>266724.065424825</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>228776.172941884</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>248878.757970612</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>263800.441865593</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>245408.441913052</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>236971.442808517</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>238014.691525358</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>466242.291514899</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>459169.636178279</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>459047.103328985</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>515211.428718561</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>595415.300067081</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>635859.009815687</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>717484.419754137</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>806713.877676542</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>882933.018575956</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>697164.443595809</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>830291.866542988</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>955792.170768514</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>836315.566710241</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>802527.362675785</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>799327.179244097</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.841639030028478</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.803002778921019</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.739435058250548</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.583241996265242</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.484406903526881</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.492208937182249</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.453918705305924</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.557899207023187</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.551115458216968</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.670918267048185</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.735068773397229</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.704720376826934</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.891952642526701</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.895216961506812</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.865262405907649</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>200432.483795589</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>204291.456562131</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>228417.54872117</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>281023.060194247</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>322758.324484707</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>337639.871728225</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>355743.557342027</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>407495.116942883</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>456595.942387498</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>455977.157012489</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>462667.013073372</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>503512.91320175</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>470186.405313954</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>484178.128296644</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>481118.712384928</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.0827197921178</t>
+          <t>921.13550344716</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656989727557</t>
+          <t>934.358088271322</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.0575296108291</t>
+          <t>960.920647860278</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884016973125884</t>
+          <t>1043.74032567922</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923144947343</t>
+          <t>1115.91542869107</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793907242183</t>
+          <t>1103.32939238848</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796431984708506</t>
+          <t>1135.95624505775</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660707770887</t>
+          <t>1060.08683975136</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.67990209409845</t>
+          <t>1065.56375048937</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.71694866647548</t>
+          <t>967.224977642001</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.75431847325941</t>
+          <t>931.233515741297</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.718390804597701</t>
+          <t>947.339981765332</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.778331257783312</t>
+          <t>835.040495965415</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.75295534974776</t>
+          <t>826.502668397687</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.75273011658591</t>
+          <t>840.43484338096</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.423</t>
+          <t>21759813715.526</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.432</t>
+          <t>23073594549.071</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.478</t>
+          <t>23515547442.2058</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>26100775854.0074</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.679</t>
+          <t>28809845292.5334</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.708</t>
+          <t>26906718217.4091</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.747</t>
+          <t>27518935708.1868</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.846</t>
+          <t>27254703101.8031</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>26332196344.1343</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.885</t>
+          <t>21829487043.9797</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.852</t>
+          <t>19982556084.2318</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.907</t>
+          <t>22066806870.583</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.826</t>
+          <t>21590629203.9484</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.847</t>
+          <t>22831440737.146</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.856</t>
+          <t>24132209133.0481</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.569</t>
+          <t>23178319225.6314</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.579</t>
+          <t>24425210333.7348</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.638</t>
+          <t>25236107994.9423</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.797</t>
+          <t>27940345496.8548</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.912</t>
+          <t>30385788192.3969</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.943</t>
+          <t>28704197741.5912</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.991</t>
+          <t>29596197248.737</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>29712209300.2134</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>28926295089.3909</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.166</t>
+          <t>24169908411.5595</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1.126</t>
+          <t>22354083635.2086</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1.199</t>
+          <t>24109349370.9526</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1.092</t>
+          <t>22793814655.4562</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1.119</t>
+          <t>24345282292.3862</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>25510867436.3839</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.223</t>
+          <t>-1418505510.10541</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3.259</t>
+          <t>-1351615784.66381</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3.627</t>
+          <t>-1720560552.73655</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>4.521</t>
+          <t>-1839569642.84738</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>-1575942899.8635</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>5.552</t>
+          <t>-1797479524.18211</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>5.862</t>
+          <t>-2077261540.55025</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>6.748</t>
+          <t>-2457506198.41034</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>7.619</t>
+          <t>-2594098745.25655</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>7.395</t>
+          <t>-2340421367.57982</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>7.251</t>
+          <t>-2371527550.97677</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>7.942</t>
+          <t>-2042542500.36958</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>-1203185451.50774</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>7.675</t>
+          <t>-1513841555.24025</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>7.666</t>
+          <t>-1378658303.33577</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2.214</t>
+          <t>1696.39909509322</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2.258</t>
+          <t>1684.65022966052</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2.456</t>
+          <t>1671.459063085</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>3.024</t>
+          <t>1652.4935168109</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>1656.47256610118</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>3.609</t>
+          <t>1646.39797997795</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>3.835</t>
+          <t>1651.58803309855</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>4.399</t>
+          <t>1651.50844702436</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>4.805</t>
+          <t>1652.81240509971</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>4.159</t>
+          <t>1616.15388348729</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>4.134</t>
+          <t>1615.75419390364</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>4.475</t>
+          <t>1614.94977069822</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>4.025</t>
+          <t>1579.85707295857</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>4.098</t>
+          <t>1566.40187587794</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>4.075</t>
+          <t>1567.63151797339</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.026</t>
+          <t>1712.33549595858</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1701.35206538197</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.149</t>
+          <t>1687.00309502199</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.424</t>
+          <t>1668.31626843618</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.628</t>
+          <t>1673.19475693467</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1.672</t>
+          <t>1660.63227998631</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1.743</t>
+          <t>1668.84524859689</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.982</t>
+          <t>1669.40726548329</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2.168</t>
+          <t>1672.04587897064</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.984</t>
+          <t>1637.61023821373</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1.915</t>
+          <t>1635.91288058297</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2.049</t>
+          <t>1635.06992297689</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1.862</t>
+          <t>1597.99935966649</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>1.921</t>
+          <t>1582.75056938647</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>1583.30391527096</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>267627.510954046</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>274969.724117942</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>286445.036477525</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>338256.862845293</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>400220.91085869</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>424049.804870191</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>474750.650374909</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>565788.235954336</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>605293.804857215</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>454801.408079581</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>498271.291295663</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>573539.229347708</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>551593.599402072</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>572563.183765121</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>588585.234177635</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>9723780393.11407</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10029940125.4539</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>9737574798.81363</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>9881217501.64174</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>10630892010.7351</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>10812925131.5777</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>12160018786.4203</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>12491955484.1662</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>12472584766.8037</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>10112715255.0762</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>12162333540.9808</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>14001330973.9737</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>13268865311.1794</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>13150324842.3642</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>13671512014.8996</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>257864.189178019</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>260144.841435637</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>275403.82041267</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>328607.628966199</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>388108.001460652</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>421866.091499784</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>485487.177581681</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>560698.185031403</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>610976.165850856</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>458019.36643647</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>525350.127880005</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>594416.906679322</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>522713.403737011</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>519665.697077959</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>519897.473813911</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>39420.189</t>
+          <t>29975151634.8041</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>39936.347</t>
+          <t>30730220850.1426</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>40264.378</t>
+          <t>31470235641.2577</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>40403.117</t>
+          <t>34513895380.5978</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>40766.721</t>
+          <t>37769216536.8501</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>40687.65</t>
+          <t>37444294412.3331</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>41694.096</t>
+          <t>40911153017.3758</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>42227.49</t>
+          <t>39248848036.9826</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>42385.025</t>
+          <t>39293984001.86</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>40818.254</t>
+          <t>32255470031.7045</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>40514.528</t>
+          <t>34486742668.7443</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>40619.552</t>
+          <t>37781137146.3858</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>39574.135</t>
+          <t>32464487292.1618</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>38497.084</t>
+          <t>31570638691.8599</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>38582.425</t>
+          <t>32131756052.2978</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>28269.982</t>
+          <t>9763.32177602757</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>28718.064</t>
+          <t>14824.8826823055</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>29107.791</t>
+          <t>11041.2160648548</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>29121.067</t>
+          <t>9649.23387909359</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>29263.41</t>
+          <t>12112.9093980381</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>29569.637</t>
+          <t>2183.71337040744</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>30318.697</t>
+          <t>-10736.527206772</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>30783.622</t>
+          <t>5090.05092293359</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>31022.793</t>
+          <t>-5682.36099364068</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>29969.796</t>
+          <t>-3217.95835688926</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>29636.325</t>
+          <t>-27078.8365843419</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>29756.257</t>
+          <t>-20877.6773316139</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>29059.891</t>
+          <t>28880.1956650611</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>28323.992</t>
+          <t>52897.4866871618</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>28416.143</t>
+          <t>68687.760363724</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>57386.568</t>
+          <t>-20251371241.69</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>57046.776</t>
+          <t>-20700280724.6888</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>56706.19</t>
+          <t>-21732660842.444</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>58474.886</t>
+          <t>-24632677878.9561</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>61120.938</t>
+          <t>-27138324526.115</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>60788.936</t>
+          <t>-26631369280.7554</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>64928.591</t>
+          <t>-28751134230.9556</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>64661.419</t>
+          <t>-26756892552.8163</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>65194.909</t>
+          <t>-26821399235.0563</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>56578.123</t>
+          <t>-22142754776.6283</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>60811.676</t>
+          <t>-22324409127.7635</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>65923.151</t>
+          <t>-23779806172.4121</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>59194.135</t>
+          <t>-19195621980.9824</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>56853.877</t>
+          <t>-18420313849.4957</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>56363.405</t>
+          <t>-18460244037.3982</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>439873.45892</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.459</t>
+          <t>445643.57432</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.459</t>
+          <t>485570.04432</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.515</t>
+          <t>592539.64112</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>677124.80157</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>690752.06343</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.718</t>
+          <t>724394.06136</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.807</t>
+          <t>824765.8036</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.883</t>
+          <t>897812.64876</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.697</t>
+          <t>795299.33824</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>766016.50428</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.956</t>
+          <t>813461.2752</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.836</t>
+          <t>735607.48624</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.802</t>
+          <t>759378.22899</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.799</t>
+          <t>758926.205515587</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>18959.061</t>
+          <t>0.0796157598728694</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>19140.995</t>
+          <t>0.0817149711970259</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>19080.583</t>
+          <t>0.0778010576989733</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>19060.08</t>
+          <t>0.076441070769257</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>19270.575</t>
+          <t>0.0747440909317502</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>19252.979</t>
+          <t>0.0705664725878137</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>19568.163</t>
+          <t>0.0676088963862452</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>19757.706</t>
+          <t>0.0674309258813724</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>19695.13</t>
+          <t>0.0618649180042749</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>18563.053</t>
+          <t>0.0489934032217459</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>18227.746</t>
+          <t>0.0450123769869865</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>18193.23</t>
+          <t>0.043524331326207</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>17370.359</t>
+          <t>0.0404085603347316</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>16789.864</t>
+          <t>0.0413784090174223</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>16786.021</t>
+          <t>0.04096457412711</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>423007.13752</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>432476.82136</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>477828.79536</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>595426.57664</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>678689.50338</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>708248.46378</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>746772.4946</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>845889.45715</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>940088.73564</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>885439.82252</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>851552.52426</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>906846.7968</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>826210.68288</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>847336.96389</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>855572.287729183</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>15351.52</t>
+          <t>568761.1924</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>15928.62</t>
+          <t>579253.929</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>16736.968</t>
+          <t>638134.94496</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>18395.495</t>
+          <t>796960.15056</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>19714.664</t>
+          <t>912350.894</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>19816.589</t>
+          <t>943035.14019</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>20854.002</t>
+          <t>990578.37348</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>19761.707</t>
+          <t>1119906.67895</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>20000.757</t>
+          <t>1239736.43752</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>17937.845</t>
+          <t>1165698.93924</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>17081.58</t>
+          <t>1125835.21431</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>17456.839</t>
+          <t>1199468.7216</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>15360.157</t>
+          <t>1091793.23264</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>14944.659</t>
+          <t>1119216.96324</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>15232.965</t>
+          <t>1130163.65244963</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>84.15</t>
+          <t>3223486.7455164</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>80.29</t>
+          <t>3259007.6150888</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>73.91</t>
+          <t>3627195.4560144</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>58.31</t>
+          <t>4520792.0486736</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>48.43</t>
+          <t>5249822.9831117</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>49.22</t>
+          <t>5551876.3675518</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>45.39</t>
+          <t>5861830.2537268</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>55.77</t>
+          <t>6748424.2231475</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>55.11</t>
+          <t>7619395.1172768</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>67.08</t>
+          <t>7395407.8582296</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>7250760.9131814</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>70.46</t>
+          <t>7941866.690784</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>89.19</t>
+          <t>7430259.7360288</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>7675377.5598195</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>86.54</t>
+          <t>7665812.06199564</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.458</t>
+          <t>714018.378503729</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.454</t>
+          <t>722792.486109225</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.334</t>
+          <t>733040.537494436</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.138</t>
+          <t>737929.244396849</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.035</t>
+          <t>752693.498988022</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.989</t>
+          <t>762566.339205381</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>784499.898684378</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.835</t>
+          <t>793259.53434456</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>795345.971905736</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.851</t>
+          <t>769697.504303795</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.891</t>
+          <t>784356.49388</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.871</t>
+          <t>786825.328958683</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.882</t>
+          <t>771326.355977091</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.834</t>
+          <t>756298.155419903</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>0.841</t>
+          <t>759791.94261549</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>533429.188591612</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>541411.251530357</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>550585.946893399</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>552828.544498996</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>560860.451785949</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>573237.964965407</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>590387.272052476</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>597487.145289583</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>602192.584367672</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>584506.273787348</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>593266.88648</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>596517.212743283</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>588305.659950085</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>576331.671373098</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>579641.60693796</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>457072.83048</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>470601.16996</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>510617.19168</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>626597.24512</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>715151.57091</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>729416.20323</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>752055.4316</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>862547.61055</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>927969.19656</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>818303.3562</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>789040.99674</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>849177.3504</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>770432.50416</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>801773.04033</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>795145.438843042</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>28269982000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>28718064000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>29107791000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>29121067000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>29263410000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>29569637000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>30318697000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>30783622000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>31022793000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>29969796000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>29636325000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>29756257000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>29059891000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>28323992000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>28416143000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>39420189153.1113</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>39936347436.3307</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>40264377670.1278</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>40403116557.3606</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>40766720974.8105</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>40687649681.6286</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>41694095921.8949</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>42227489839.6732</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>42385025395.2026</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>40818253992.5964</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>40514527626.6537</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>40619551575.538</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>39574134542.2686</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>38497083824.1301</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>38582424798.4972</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>18959061376.1308</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>19140994539.6157</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>19080582855.3485</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>19060080257.6334</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>19270575175.6172</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>19252979005.1711</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>19568162577.9429</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>19757706413.5773</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>19695130102.4615</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>18563053284.1125</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>18227745962.5505</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>18193230448.5615</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>17370358665.3057</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>16789864091.5348</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>16786021262.2449</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>23021300</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>23473300</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>23867400</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>24217900</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>24364600</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>24501300</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>24983800</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>25294900</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>25349200</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>24925500</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>24765700</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>24842700</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>24764800</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>24322900</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>24368300</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>16664700</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>17046900</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>17414600</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>17622500</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>17666100</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>17960200</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>18357300</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>18639700</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>18769700</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>18543900</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>18342100</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>18425500</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>18394000</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>18082200</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>18126800</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>39420189153.1113</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>39936347436.3307</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>40264377670.1278</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>40403116557.3606</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>40766720974.8105</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>40687649681.6286</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>41694095921.8949</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>42227489839.6732</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>42385025395.2026</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>40818253992.5964</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>40514527626.6537</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>40619551575.538</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>39574134542.2686</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>38497083824.1301</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>38582424798.4972</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>28269982000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>28718064000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>29107791000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>29121067000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>29263410000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>29569637000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>30318697000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>30783622000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>31022793000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>29969796000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>29636325000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>29756257000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>29059891000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>28323992000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>28416143000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2213740.26544</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2258374.067</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2455603.48704</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>3023639.3432</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>3470152.36162</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>3609145.17249</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>3835137.03448</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>4399257.3066</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>4805338.1926</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>4158508.3276</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>4133509.79796</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>4475042.9424</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>4024546.7064</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>4098209.01204</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>4075402.11906248</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1025834.02288</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1049855.09896</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1148752.04208</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1423557.39568</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>1627502.5893</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>1672451.34342</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>1742633.80508</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1982454.2895</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2167705.63408</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1984002.29544</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1914876.34362</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>2048646.072</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1862225.7368</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>1920990.00357</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1925309.48981919</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>4485170.4457519</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>4492337.29528196</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>4532539.70567284</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>4544380.26635142</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>4589189.86635431</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>4716014.74997088</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>4756020.02003363</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>4863293.35712624</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>4939001.93393815</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>4992843.1625015</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>5051522.0482872</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>5145949.6473222</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>5087383.36510586</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>5021241.47972148</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>5005434.29698804</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
